--- a/conditions/training_sounds.xlsx
+++ b/conditions/training_sounds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pahr0811/Documents/PhD/Year_1/Study_1/PsychoPy_experiment/creaky_experiment/conditions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42964112-5908-5A4E-B2A0-7156EE67513A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CC42C5-E126-FE46-B2D5-C17C5DD71E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11980" yWindow="5980" windowWidth="27640" windowHeight="16680" xr2:uid="{0DF22297-7E3B-0E42-B29C-48ED2A056DFB}"/>
+    <workbookView xWindow="18600" yWindow="3760" windowWidth="27640" windowHeight="16680" xr2:uid="{0DF22297-7E3B-0E42-B29C-48ED2A056DFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>trainFile</t>
   </si>
@@ -53,34 +53,40 @@
     <t>creaky</t>
   </si>
   <si>
-    <t>training_stimuli/chat_creaky.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/chat_modal.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/zat_modal.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/zat_creaky.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/vop_modal.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/vop_creaky.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/jat_creaky.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/jat_modal.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/vak_creaky.wav</t>
-  </si>
-  <si>
-    <t>training_stimuli/vak_modal.wav</t>
+    <t>training_stimuli/chat_f_creaky.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/chat_f_modal.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vop_m_creaky.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vop_m_modal.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/jat_m_creaky.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vak_m_modal.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vak_m_creaky.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vop_f_modal.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vop_f_creaky.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/zat_m_creaky.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vok_f_modal.wav</t>
+  </si>
+  <si>
+    <t>training_stimuli/vok_f_creaky.wav</t>
   </si>
 </sst>
 </file>
@@ -452,10 +458,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4A4789-3615-BD43-927D-D985B7A43789}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -471,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -479,12 +485,12 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -492,7 +498,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -503,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -511,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -543,11 +549,28 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
